--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2019_o_higgins.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2019_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:04</t>
+    <t xml:space="preserve">2026-09-24 00:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -675,19 +675,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="9">
@@ -698,19 +698,19 @@
         <v>16</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.07</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -721,19 +721,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="11">
@@ -744,19 +744,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.17</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="12">
@@ -799,7 +799,7 @@
         <v>0.06</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.4</v>
@@ -819,13 +819,13 @@
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>-0.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.06</v>
